--- a/output/pdf_financials_xlsx/SIEN.xlsx
+++ b/output/pdf_financials_xlsx/SIEN.xlsx
@@ -1041,28 +1041,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.013176</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000118</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000664</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00433</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.00382</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000189</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>9.8e-05</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1071,25 +1071,25 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.008278000000000001</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.005349</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.003207</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.001117</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.074726</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.028639</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.009509</v>
       </c>
     </row>
     <row r="13">
@@ -2069,28 +2069,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.630746</v>
+        <v>-0.643922</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.753894</v>
+        <v>-0.754012</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.038679</v>
+        <v>-1.039343</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.287877</v>
+        <v>-1.292207</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.62371</v>
+        <v>-1.62753</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.352434</v>
+        <v>-0.352623</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-2.027214</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.380637</v>
+        <v>-0.380735</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.833693</v>
@@ -2099,25 +2099,25 @@
         <v>-0.683341</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.938367</v>
+        <v>-0.946645</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.414746</v>
+        <v>-0.420095</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.973154</v>
+        <v>-0.976361</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.157282</v>
+        <v>-1.158399</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.294043</v>
+        <v>-1.368769</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.633802</v>
+        <v>-1.662441</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.7372030000000001</v>
+        <v>-0.746712</v>
       </c>
     </row>
     <row r="28">
@@ -2185,28 +2185,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.630746</v>
+        <v>-0.643922</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.753894</v>
+        <v>-0.754012</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.034543</v>
+        <v>-1.035207</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.284323</v>
+        <v>-1.288653</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.620543</v>
+        <v>-1.624363</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.350082</v>
+        <v>-0.350271</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-2.02557</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.379485</v>
+        <v>-0.379583</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.832885</v>
@@ -2215,25 +2215,25 @@
         <v>-0.681461</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.938367</v>
+        <v>-0.946645</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.414746</v>
+        <v>-0.420095</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.973154</v>
+        <v>-0.976361</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.157282</v>
+        <v>-1.158399</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.294043</v>
+        <v>-1.368769</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.633802</v>
+        <v>-1.662441</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.7372030000000001</v>
+        <v>-0.746712</v>
       </c>
     </row>
     <row r="30">
@@ -2510,13 +2510,13 @@
         <v>0.009684999999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.020028</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.002454</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.018618</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.203003</v>
@@ -2628,13 +2628,13 @@
         <v>0.009684999999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.020028</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.002454</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.018618</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.203003</v>
@@ -3348,13 +3348,13 @@
         <v>0.225665</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.053822</v>
+        <v>0.033794</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.054159</v>
+        <v>0.051705</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.175731</v>
+        <v>0.157113</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.156205</v>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -34883,7 +34883,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -43010,7 +43010,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -44616,7 +44616,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -46335,7 +46335,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E386" s="5" t="n">

--- a/output/pdf_financials_xlsx/SIEN.xlsx
+++ b/output/pdf_financials_xlsx/SIEN.xlsx
@@ -747,55 +747,55 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.064525</v>
+        <v>0.334525</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.07768799999999999</v>
+        <v>0.347688</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.066757</v>
+        <v>0.336757</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.086133</v>
+        <v>0.401133</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.069012</v>
+        <v>0.429012</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.079197</v>
+        <v>0.439197</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.079179</v>
+        <v>0.414179</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.053935</v>
+        <v>0.106435</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.08814</v>
+        <v>0.18564</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.153041</v>
+        <v>0.273041</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.110313</v>
+        <v>0.230313</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.099992</v>
+        <v>0.219992</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.120833</v>
+        <v>0.302333</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.119101</v>
+        <v>0.293101</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.239926</v>
+        <v>0.441426</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.181077</v>
+        <v>0.403477</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.142666</v>
+        <v>0.376166</v>
       </c>
     </row>
     <row r="8">
@@ -1811,77 +1811,49 @@
         <v>-0.01</v>
       </c>
       <c r="D24" s="3" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>-0.103</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M24" s="3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="25">
@@ -1897,77 +1869,49 @@
         <v>-0.01</v>
       </c>
       <c r="D25" s="3" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>-0.103</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M25" s="3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="26">
@@ -1986,50 +1930,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D26" s="3" t="n">
+        <v>86.556583</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>99.06746200000001</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>11.597929</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>13.555154</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>19.681689</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>25.3758</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>27.789767</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>34.16705</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>46.91835</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -2051,15 +1977,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q26" s="3" t="n">
+        <v>20.422525</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>24.573433</v>
       </c>
     </row>
     <row r="27">
@@ -2847,13 +2769,11 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0.031549</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>1e-06</v>
@@ -2907,58 +2827,56 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.031549</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.000407</v>
+        <v>0.007823</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>0.116397</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.033405</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>0.225565</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.033794</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>0.050838</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>0.016086</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>0.025348</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
+        <v>0.010145</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0</v>
+        <v>0.023029</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>0.015613</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0</v>
+        <v>0.011263</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0</v>
+        <v>0.005192</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>0</v>
+        <v>0.004916</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>0</v>
+        <v>0.007898000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3336,49 +3254,49 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.009466</v>
+        <v>0.00205</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.118607</v>
+        <v>0.00221</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.033985</v>
+        <v>0.00058</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.225665</v>
+        <v>0.0001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.033794</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.051705</v>
+        <v>0.000867</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.157113</v>
+        <v>0.141027</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.156205</v>
+        <v>0.130857</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.013832</v>
+        <v>0.003687</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.028791</v>
+        <v>0.005762</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.0183</v>
+        <v>0.002687</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.014083</v>
+        <v>0.00282</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.045978</v>
+        <v>0.040786</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.018616</v>
+        <v>0.0137</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.02053</v>
+        <v>0.012632</v>
       </c>
     </row>
     <row r="49">
@@ -3449,43 +3367,41 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0.413001</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0</v>
+        <v>0.413001</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0</v>
+        <v>0.413001</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0</v>
+        <v>0.413001</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0</v>
+        <v>0.413001</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0</v>
+        <v>0.413001</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0</v>
+        <v>0.413001</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0</v>
+        <v>0.413001</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0</v>
+        <v>0.413001</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0</v>
+        <v>0.413</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0</v>
+        <v>0.413</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>0</v>
+        <v>0.413</v>
       </c>
       <c r="N50" s="3" t="n">
         <v>0</v>
@@ -3629,34 +3545,32 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0.007046</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.012549</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0</v>
+        <v>0.012549</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0</v>
+        <v>0.010152</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0</v>
+        <v>0.007835999999999999</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0</v>
+        <v>0.005484</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0</v>
+        <v>0.00384</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0</v>
+        <v>0.002688</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0</v>
+        <v>0.00188</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>0</v>
@@ -4150,34 +4064,34 @@
         <v>0</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.425551</v>
+        <v>0.01255</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0.441563</v>
+        <v>0.028562</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.427312</v>
+        <v>0.014311</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.42496</v>
+        <v>0.011959</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.423316</v>
+        <v>0.010315</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.422164</v>
+        <v>0.009162999999999999</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.421356</v>
+        <v>0.008355</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.413</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.413</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.413</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3" t="n">
         <v>0</v>
@@ -4572,49 +4486,49 @@
         <v>0.15993</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.213434</v>
+        <v>0.15993</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>0.486491</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>1.08523</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>1.353609</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>1.487992</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>1.525858</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>1.597282</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>0.906673</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>0.959129</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>0.916373</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>0.06457499999999999</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>0.205085</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0</v>
+        <v>0.142385</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0</v>
+        <v>0.076969</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>0</v>
+        <v>0.086814</v>
       </c>
     </row>
     <row r="69">
@@ -4635,37 +4549,37 @@
         <v>0</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="M69" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>0</v>
+        <v>0.036208</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="P69" s="3" t="n">
         <v>0</v>
@@ -4755,37 +4669,37 @@
         <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="M71" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.036208</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>0</v>
@@ -4995,46 +4909,46 @@
         <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.810605</v>
+        <v>0.199114</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.232792</v>
+        <v>0.017562</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1.496441</v>
+        <v>0.012832</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>1.493557</v>
+        <v>0.000565</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>1.532673</v>
+        <v>0.000815</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>1.603348</v>
+        <v>0.001066</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>1.952989</v>
+        <v>1.001316</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.965695</v>
+        <v>0.001566</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.916373</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.071552</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.245085</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.142385</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.160302</v>
+        <v>0.083333</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>0.103421</v>
+        <v>0.016607</v>
       </c>
     </row>
     <row r="76">
@@ -5300,60 +5214,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E80" s="3" t="n">
+        <v>0.04804779871893037</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.1048267898569598</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.1102237627170666</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>-0.009992106236073502</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>-0.007920718884445952</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>-0.007032694999050586</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>-0.1150942238045547</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.004317021324358534</v>
       </c>
       <c r="M80" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N80" s="3" t="n">
+        <v>0.01850965765721553</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.04197773920489964</v>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
@@ -5807,52 +5701,52 @@
         </is>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>12.116445</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>12.116445</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>15.504243</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>15.513618</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>15.80533</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>16.15273</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>16.276255</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>16.880593</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>17.656593</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0</v>
+        <v>19.877725</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0</v>
+        <v>20.332586</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>0</v>
+        <v>23.713111</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>0</v>
+        <v>23.868993</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>0</v>
+        <v>26.966903</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>0</v>
+        <v>27.186</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>0</v>
+        <v>29.661008</v>
       </c>
     </row>
     <row r="89">
@@ -6039,58 +5933,56 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>10.87264</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.904314</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.904314</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.380576</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.633476</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.633476</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.633476</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.633476</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.909373</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.962695</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.40312</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.505697</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.311555</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.309673</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.899366</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>5.064914</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>5.088898</v>
       </c>
     </row>
     <row r="93">
@@ -8828,7 +8720,11 @@
           <t>Receivables – Note 5</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>-</t>
@@ -9346,7 +9242,11 @@
           <t>Accounts payable and accrued liabilities – Notes 7 and 11 $</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -9617,7 +9517,11 @@
           <t>Share capital – Note 9</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -9712,7 +9616,11 @@
           <t>Reserves – Note 9</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10068,7 +9976,11 @@
           <t>Loans payable – Note 8</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10169,7 +10081,11 @@
           <t>Accounts payable and accrued liabilities – Notes 7 and 12 $</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -10268,7 +10184,11 @@
           <t>Loans payable – Note 9</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -10361,7 +10281,11 @@
           <t>Loans payable – Note 9</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -10565,7 +10489,11 @@
           <t>Share capital – Note 10</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -10664,7 +10592,11 @@
           <t>Reserves – Note 10</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10763,7 +10695,11 @@
           <t>Prepaid expenses – Note 6</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -10860,7 +10796,11 @@
           <t>Investments – Note 7</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11050,7 +10990,11 @@
           <t>Accounts payable and accrued liabilities – Notes 9 and 13 $</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -11149,7 +11093,11 @@
           <t>Interest payable – Note 10</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>InterestPayable</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -11246,7 +11194,11 @@
           <t>Loans payable – Note 10</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -11343,7 +11295,11 @@
           <t>Share capital – Note 11</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -11442,7 +11398,11 @@
           <t>Reserves – Note 11</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -11541,7 +11501,11 @@
           <t>Accounts payable and accrued liabilities – Notes 9 and 13 $ 959,129 $</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -11640,7 +11604,11 @@
           <t>Share capital – Note 11</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -11735,7 +11703,11 @@
           <t>Reserves – Note 11</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -12325,7 +12297,11 @@
           <t>Receivables – Note 4</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -12418,7 +12394,11 @@
           <t>Prepaid expenses – Note 5</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -12517,7 +12497,11 @@
           <t>Equipment – Note 7</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -12612,7 +12596,11 @@
           <t>Investments – Note 6</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -12796,7 +12784,11 @@
           <t>Accounts payable and accrued liabilities – Notes 9 and 13 $ 1,</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -12895,7 +12887,11 @@
           <t>Share capital – Note 11</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -12994,7 +12990,11 @@
           <t>Reserves – Note 11</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -13491,7 +13491,11 @@
           <t>Equipment – Note 6</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -13586,7 +13590,11 @@
           <t>Investments – Note 5</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -13780,7 +13788,11 @@
           <t>Accounts payable and accrued liabilities – Notes 8 and 12 $</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -13877,7 +13889,11 @@
           <t>Interest payable – Note 9</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>InterestPayable</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -13972,7 +13988,11 @@
           <t>Share capital – Note 10</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -14069,7 +14089,11 @@
           <t>Reserves – Note 10</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -14166,7 +14190,11 @@
           <t>Accounts payable and accrued liabilities – Notes 8 and 13 $</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -14265,7 +14293,11 @@
           <t>Accounts payable and accrued liabilities – Notes 9 and 14 $</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -14362,7 +14394,11 @@
           <t>Interest payable – Notes 10 and 14</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>InterestPayable</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -14459,7 +14495,11 @@
           <t>Loans payable – Notes 10 and 14</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -14655,7 +14695,11 @@
           <t>Share capital – Note 12</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -14752,7 +14796,11 @@
           <t>Reserves – Note 12</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -15053,7 +15101,11 @@
           <t>Receivables – Note 5 116,397</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -15358,7 +15410,11 @@
           <t>Equipment – Note 7 10,152</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -15457,7 +15513,11 @@
           <t>Investments – Note 6 413,001</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -16073,7 +16133,11 @@
           <t>Accounts payable and accrued liabilities – Notes 9 and 14 $ 486,491 $</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -16172,7 +16236,11 @@
           <t>Interest payable – Notes 10 and 14 4,668</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>InterestPayable</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -16275,7 +16343,11 @@
           <t>Loans payable – Notes 10 and 14 125,000</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -16584,7 +16656,11 @@
           <t>Share capital – Note 12 15,504,243</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -16683,7 +16759,11 @@
           <t>Reserves – Note 12 2,380,576</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -17590,7 +17670,11 @@
           <t>Other receivables – Note 8</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>0.031549</v>
       </c>
@@ -17689,7 +17773,11 @@
           <t>Equipment – Note 5</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
         <v>0.007046</v>
       </c>
@@ -17786,7 +17874,11 @@
           <t>Long-term investments – Note 4</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E95" s="5" t="n">
         <v>0.413001</v>
       </c>
@@ -17980,7 +18072,11 @@
           <t>Mineral properties – Note 6</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -18180,7 +18276,11 @@
           <t>Share capital – Note 7</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -18279,7 +18379,11 @@
           <t>Contributed surplus – Note 7</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -18683,7 +18787,11 @@
           <t>Contributed surplus – Note 7</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E104" s="5" t="n">
         <v>10.87264</v>
       </c>
@@ -30785,7 +30893,11 @@
           <t>Cash and cash equivalents, end of the year – Note 4 $</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -34094,7 +34206,11 @@
           <t>Management fees – Note 11</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -34272,7 +34388,11 @@
           <t>Professional fees – Note 11</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -35368,7 +35488,11 @@
           <t>Loss per share – basic and diluted – Note 10 $</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -36045,7 +36169,11 @@
           <t>Loss per share – basic and diluted – Note 10 $</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -36241,7 +36369,11 @@
           <t>Interest expense – Note 8</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -36736,7 +36868,11 @@
           <t>Management fees – Note 12</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -36829,7 +36965,11 @@
           <t>Professional fees – Note 12</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -37021,7 +37161,11 @@
           <t>Interest expense – Note 9</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -37514,7 +37658,11 @@
           <t>Loss per share – basic and diluted – Note 11 $</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -37803,7 +37951,11 @@
           <t>Management fees – Note 13</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -37894,7 +38046,11 @@
           <t>Professional fees – Note 13</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -38080,7 +38236,11 @@
           <t>Interest expense – Note 10</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -38464,7 +38624,11 @@
           <t>Loss per share – basic and diluted – Note 12 $</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -38850,7 +39014,11 @@
           <t>Depreciation – Note 7</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -39141,7 +39309,11 @@
           <t>Depreciation – Note 6</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -39529,7 +39701,11 @@
           <t>Loss per share – basic and diluted – Note 11 $</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -40620,7 +40796,11 @@
           <t>Management fees – Note 14</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -41416,7 +41596,11 @@
           <t>Loss per share – basic and diluted – Note 13 $</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -42218,7 +42402,11 @@
           <t>Management fees – Note 14</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -43111,7 +43299,11 @@
           <t>Interest expense – Note 10</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -43618,7 +43810,11 @@
           <t>Loss per share – basic and diluted – Note 13 $</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -44319,7 +44515,11 @@
           <t>Management fees – Note 8</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E366" s="5" t="n">
         <v>0.27</v>
       </c>

--- a/output/pdf_financials_xlsx/SIEN.xlsx
+++ b/output/pdf_financials_xlsx/SIEN.xlsx
@@ -747,55 +747,55 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.334525</v>
+        <v>0.367983</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.347688</v>
+        <v>0.378653</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.336757</v>
+        <v>0.367722</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.401133</v>
+        <v>0.431133</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.429012</v>
+        <v>0.459012</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.439197</v>
+        <v>0.469197</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.414179</v>
+        <v>0.443346</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.106435</v>
+        <v>0.113935</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.18564</v>
+        <v>0.20064</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.273041</v>
+        <v>0.285541</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.230313</v>
+        <v>0.242813</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.219992</v>
+        <v>0.232492</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.302333</v>
+        <v>0.317333</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.293101</v>
+        <v>0.305601</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.441426</v>
+        <v>0.453926</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.403477</v>
+        <v>0.415977</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.376166</v>
+        <v>0.388666</v>
       </c>
     </row>
     <row r="8">
@@ -4431,46 +4431,46 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.035714</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.034214</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.025014</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.025014</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.026814</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.031014</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.03426</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.033214</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.033214</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.046527</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.036514</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.040389</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.041914</v>
       </c>
     </row>
     <row r="68">
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>-0.008309</v>
+        <v>-0.016291</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0.031548</v>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.011892</v>
+        <v>0.00391</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.050194</v>
@@ -33509,7 +33509,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E254" s="5" t="n">
         <v>-0.007982</v>
       </c>
@@ -34012,7 +34016,11 @@
           <t>Directors’ fees – Note 11</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -36775,7 +36783,11 @@
           <t>Directors’ fees – Note 12</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -37860,7 +37872,11 @@
           <t>Directors’ fees – Note 13</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -40699,7 +40715,11 @@
           <t>Directors’ fees – Note 14</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -42202,7 +42222,11 @@
           <t>Directors’ fees – Note 14</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -44216,7 +44240,11 @@
           <t>Directors’ fees – Note 8</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E363" s="5" t="n">
         <v>0.033458</v>
       </c>
